--- a/進捗管理表/進捗管理表_富.xlsx
+++ b/進捗管理表/進捗管理表_富.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN02\Documents\project\MyTaskSystem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN02\Documents\project\MyTaskSystem\進捗管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91DBA302-295D-40F0-9A51-1F27E9E50D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6EEA66-4010-44A6-8EF3-349E7CA4C651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小工程" sheetId="1" r:id="rId1"/>
@@ -212,9 +212,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>未着手</t>
-  </si>
-  <si>
     <t>富</t>
     <rPh sb="0" eb="1">
       <t>トミ</t>
@@ -251,6 +248,9 @@
       <t>ガメンセッケイショ</t>
     </rPh>
     <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>作成完了</t>
   </si>
 </sst>
 </file>
@@ -337,7 +337,7 @@
       <name val="MS PGothic"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,6 +377,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1123,81 +1129,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1269,6 +1200,87 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1579,142 +1591,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="96" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="67">
+      <c r="G3" s="85">
         <v>45705</v>
       </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="68"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="68"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="69"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="86"/>
+      <c r="U3" s="86"/>
+      <c r="V3" s="86"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="86"/>
+      <c r="Y3" s="86"/>
+      <c r="Z3" s="86"/>
+      <c r="AA3" s="86"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="86"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="86"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86"/>
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="86"/>
+      <c r="AJ3" s="86"/>
+      <c r="AK3" s="86"/>
+      <c r="AL3" s="87"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="58" t="s">
+      <c r="A4" s="95"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
-      <c r="U4" s="71"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="71"/>
-      <c r="AC4" s="71"/>
-      <c r="AD4" s="71"/>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="71"/>
-      <c r="AH4" s="71"/>
-      <c r="AI4" s="71"/>
-      <c r="AJ4" s="71"/>
-      <c r="AK4" s="71"/>
-      <c r="AL4" s="72"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
+      <c r="AB4" s="89"/>
+      <c r="AC4" s="89"/>
+      <c r="AD4" s="89"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
+      <c r="AH4" s="89"/>
+      <c r="AI4" s="89"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="89"/>
+      <c r="AL4" s="90"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="62">
+      <c r="A5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="79">
         <v>17</v>
       </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="59">
+      <c r="H5" s="80"/>
+      <c r="I5" s="81">
         <v>18</v>
       </c>
-      <c r="J5" s="60"/>
-      <c r="K5" s="59">
+      <c r="J5" s="98"/>
+      <c r="K5" s="81">
         <v>19</v>
       </c>
-      <c r="L5" s="60"/>
-      <c r="M5" s="59">
+      <c r="L5" s="98"/>
+      <c r="M5" s="81">
         <v>20</v>
       </c>
-      <c r="N5" s="60"/>
-      <c r="O5" s="59">
+      <c r="N5" s="98"/>
+      <c r="O5" s="81">
         <v>21</v>
       </c>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="59">
+      <c r="P5" s="98"/>
+      <c r="Q5" s="81">
         <v>25</v>
       </c>
-      <c r="R5" s="61"/>
-      <c r="S5" s="62">
+      <c r="R5" s="99"/>
+      <c r="S5" s="79">
         <v>26</v>
       </c>
-      <c r="T5" s="63"/>
-      <c r="U5" s="59">
+      <c r="T5" s="80"/>
+      <c r="U5" s="81">
         <v>27</v>
       </c>
-      <c r="V5" s="63"/>
-      <c r="W5" s="59">
+      <c r="V5" s="80"/>
+      <c r="W5" s="81">
         <v>28</v>
       </c>
-      <c r="X5" s="63"/>
+      <c r="X5" s="80"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1731,48 +1743,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="62" t="s">
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="63"/>
-      <c r="I6" s="74" t="s">
+      <c r="H6" s="80"/>
+      <c r="I6" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="63"/>
-      <c r="K6" s="59" t="s">
+      <c r="J6" s="80"/>
+      <c r="K6" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="63"/>
-      <c r="M6" s="59" t="s">
+      <c r="L6" s="80"/>
+      <c r="M6" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="63"/>
-      <c r="O6" s="59" t="s">
+      <c r="N6" s="80"/>
+      <c r="O6" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="63"/>
-      <c r="Q6" s="59" t="s">
+      <c r="P6" s="80"/>
+      <c r="Q6" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="63"/>
-      <c r="S6" s="75" t="s">
+      <c r="R6" s="80"/>
+      <c r="S6" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="63"/>
-      <c r="U6" s="76" t="s">
+      <c r="T6" s="80"/>
+      <c r="U6" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="63"/>
-      <c r="W6" s="76" t="s">
+      <c r="V6" s="80"/>
+      <c r="W6" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="63"/>
+      <c r="X6" s="80"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -1831,13 +1843,13 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="54">
+      <c r="A8" s="76">
         <v>1</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
       <c r="F8" s="21" t="s">
         <v>13</v>
       </c>
@@ -1875,11 +1887,11 @@
       <c r="AL8" s="27"/>
     </row>
     <row r="9" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
+      <c r="A9" s="77"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
       <c r="F9" s="28" t="s">
         <v>14</v>
       </c>
@@ -1917,13 +1929,13 @@
       <c r="AL9" s="32"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A10" s="54">
+      <c r="A10" s="76">
         <v>2</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
       <c r="F10" s="33" t="s">
         <v>13</v>
       </c>
@@ -1961,11 +1973,11 @@
       <c r="AL10" s="10"/>
     </row>
     <row r="11" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
       <c r="F11" s="37" t="s">
         <v>14</v>
       </c>
@@ -2003,13 +2015,13 @@
       <c r="AL11" s="41"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A12" s="54">
+      <c r="A12" s="76">
         <v>3</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
       <c r="F12" s="21" t="s">
         <v>13</v>
       </c>
@@ -2047,11 +2059,11 @@
       <c r="AL12" s="27"/>
     </row>
     <row r="13" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
       <c r="F13" s="42" t="s">
         <v>14</v>
       </c>
@@ -2089,13 +2101,13 @@
       <c r="AL13" s="32"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A14" s="54">
+      <c r="A14" s="76">
         <v>4</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
       <c r="F14" s="33" t="s">
         <v>13</v>
       </c>
@@ -2133,11 +2145,11 @@
       <c r="AL14" s="10"/>
     </row>
     <row r="15" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
       <c r="F15" s="37" t="s">
         <v>14</v>
       </c>
@@ -2175,13 +2187,13 @@
       <c r="AL15" s="41"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A16" s="54">
+      <c r="A16" s="76">
         <v>5</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
       <c r="F16" s="21" t="s">
         <v>13</v>
       </c>
@@ -2219,11 +2231,11 @@
       <c r="AL16" s="27"/>
     </row>
     <row r="17" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
       <c r="F17" s="42" t="s">
         <v>14</v>
       </c>
@@ -2261,13 +2273,13 @@
       <c r="AL17" s="46"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A18" s="54">
+      <c r="A18" s="76">
         <v>6</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
       <c r="F18" s="33" t="s">
         <v>13</v>
       </c>
@@ -2305,11 +2317,11 @@
       <c r="AL18" s="10"/>
     </row>
     <row r="19" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
       <c r="F19" s="28" t="s">
         <v>14</v>
       </c>
@@ -2347,13 +2359,13 @@
       <c r="AL19" s="46"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A20" s="54">
+      <c r="A20" s="76">
         <v>7</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
       <c r="F20" s="33" t="s">
         <v>13</v>
       </c>
@@ -2391,11 +2403,11 @@
       <c r="AL20" s="10"/>
     </row>
     <row r="21" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A21" s="53"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
       <c r="F21" s="28" t="s">
         <v>14</v>
       </c>
@@ -2433,13 +2445,13 @@
       <c r="AL21" s="46"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A22" s="54">
+      <c r="A22" s="76">
         <v>8</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
       <c r="F22" s="21" t="s">
         <v>13</v>
       </c>
@@ -2477,11 +2489,11 @@
       <c r="AL22" s="27"/>
     </row>
     <row r="23" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
       <c r="F23" s="37" t="s">
         <v>14</v>
       </c>
@@ -2561,34 +2573,34 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="54">
+      <c r="A25" s="76">
         <v>1</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="78">
         <v>4</v>
       </c>
-      <c r="D25" s="52" t="s">
-        <v>32</v>
+      <c r="D25" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="E25" s="52" t="s">
-        <v>31</v>
+      <c r="E25" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="85"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="81"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
       <c r="Q25" s="24"/>
       <c r="R25" s="25"/>
       <c r="S25" s="26"/>
@@ -2613,24 +2625,24 @@
       <c r="AL25" s="27"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
       <c r="F26" s="28" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="29"/>
       <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
+      <c r="I26" s="101"/>
       <c r="J26" s="30"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
       <c r="Q26" s="30"/>
       <c r="R26" s="31"/>
       <c r="S26" s="29"/>
@@ -2655,34 +2667,34 @@
       <c r="AL26" s="32"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="54">
+      <c r="A27" s="76">
         <v>2</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="78">
         <v>4</v>
       </c>
-      <c r="D27" s="52" t="s">
-        <v>32</v>
+      <c r="D27" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="E27" s="52" t="s">
-        <v>31</v>
+      <c r="E27" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="F27" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
       <c r="Q27" s="34"/>
       <c r="R27" s="35"/>
       <c r="S27" s="36"/>
@@ -2707,24 +2719,24 @@
       <c r="AL27" s="10"/>
     </row>
     <row r="28" spans="1:38" ht="12" customHeight="1">
-      <c r="A28" s="53"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
       <c r="F28" s="37" t="s">
         <v>14</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="39"/>
       <c r="I28" s="39"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="84"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="84"/>
-      <c r="P28" s="84"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
       <c r="Q28" s="39"/>
       <c r="R28" s="40"/>
       <c r="S28" s="38"/>
@@ -2749,34 +2761,34 @@
       <c r="AL28" s="41"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="54">
+      <c r="A29" s="76">
         <v>3</v>
       </c>
-      <c r="B29" s="52" t="s">
-        <v>36</v>
+      <c r="B29" s="78" t="s">
+        <v>35</v>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="78">
         <v>2</v>
       </c>
-      <c r="D29" s="52" t="s">
-        <v>32</v>
+      <c r="D29" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="E29" s="52" t="s">
-        <v>31</v>
+      <c r="E29" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="80"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="81"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="56"/>
       <c r="Q29" s="24"/>
       <c r="R29" s="25"/>
       <c r="S29" s="26"/>
@@ -2801,11 +2813,11 @@
       <c r="AL29" s="27"/>
     </row>
     <row r="30" spans="1:38" ht="12" customHeight="1">
-      <c r="A30" s="53"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
+      <c r="A30" s="77"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
       <c r="F30" s="42" t="s">
         <v>14</v>
       </c>
@@ -2813,7 +2825,7 @@
       <c r="H30" s="44"/>
       <c r="I30" s="44"/>
       <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
+      <c r="K30" s="102"/>
       <c r="L30" s="44"/>
       <c r="M30" s="44"/>
       <c r="N30" s="44"/>
@@ -2843,31 +2855,31 @@
       <c r="AL30" s="32"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="54">
+      <c r="A31" s="76">
         <v>4</v>
       </c>
-      <c r="B31" s="52" t="s">
-        <v>33</v>
+      <c r="B31" s="78" t="s">
+        <v>32</v>
       </c>
-      <c r="C31" s="52">
+      <c r="C31" s="78">
         <v>2</v>
       </c>
-      <c r="D31" s="52" t="s">
-        <v>32</v>
+      <c r="D31" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="E31" s="52" t="s">
-        <v>31</v>
+      <c r="E31" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="F31" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="79"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="54"/>
       <c r="J31" s="50"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="78"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="53"/>
       <c r="N31" s="34"/>
       <c r="O31" s="34"/>
       <c r="P31" s="34"/>
@@ -2895,11 +2907,11 @@
       <c r="AL31" s="10"/>
     </row>
     <row r="32" spans="1:38" ht="12" customHeight="1">
-      <c r="A32" s="53"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
       <c r="F32" s="37" t="s">
         <v>14</v>
       </c>
@@ -2907,7 +2919,7 @@
       <c r="H32" s="39"/>
       <c r="I32" s="39"/>
       <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
+      <c r="K32" s="102"/>
       <c r="L32" s="39"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
@@ -2937,32 +2949,32 @@
       <c r="AL32" s="41"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="54">
+      <c r="A33" s="76">
         <v>5</v>
       </c>
-      <c r="B33" s="52" t="s">
-        <v>34</v>
+      <c r="B33" s="78" t="s">
+        <v>33</v>
       </c>
-      <c r="C33" s="52">
+      <c r="C33" s="78">
         <v>2</v>
       </c>
-      <c r="D33" s="52" t="s">
-        <v>32</v>
+      <c r="D33" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="E33" s="52" t="s">
-        <v>31</v>
+      <c r="E33" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="80"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="82"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
       <c r="J33" s="23"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="81"/>
-      <c r="N33" s="81"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
       <c r="O33" s="24"/>
       <c r="P33" s="24"/>
       <c r="Q33" s="24"/>
@@ -2989,11 +3001,11 @@
       <c r="AL33" s="27"/>
     </row>
     <row r="34" spans="1:38" ht="12" customHeight="1">
-      <c r="A34" s="53"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
       <c r="F34" s="42" t="s">
         <v>14</v>
       </c>
@@ -3001,7 +3013,7 @@
       <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
+      <c r="K34" s="102"/>
       <c r="L34" s="30"/>
       <c r="M34" s="30"/>
       <c r="N34" s="30"/>
@@ -3031,13 +3043,13 @@
       <c r="AL34" s="46"/>
     </row>
     <row r="35" spans="1:38" ht="12.75" customHeight="1">
-      <c r="A35" s="54">
+      <c r="A35" s="76">
         <v>6</v>
       </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
       <c r="F35" s="33" t="s">
         <v>13</v>
       </c>
@@ -3075,11 +3087,11 @@
       <c r="AL35" s="10"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="53"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
       <c r="F36" s="37" t="s">
         <v>14</v>
       </c>
@@ -3159,30 +3171,30 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="54">
+      <c r="A38" s="76">
         <v>1</v>
       </c>
-      <c r="B38" s="52" t="s">
+      <c r="B38" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="52">
+      <c r="C38" s="78">
         <v>8</v>
       </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
       <c r="F38" s="21" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="26"/>
       <c r="H38" s="24"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="94"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="82"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="69"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="51"/>
       <c r="S38" s="22"/>
@@ -3207,11 +3219,11 @@
       <c r="AL38" s="27"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="53"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
       <c r="F39" s="28" t="s">
         <v>14</v>
       </c>
@@ -3249,31 +3261,31 @@
       <c r="AL39" s="32"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="54">
+      <c r="A40" s="76">
         <v>2</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="52">
+      <c r="C40" s="78">
         <v>8</v>
       </c>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
       <c r="F40" s="33" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="36"/>
       <c r="H40" s="34"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="81"/>
-      <c r="M40" s="82"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="94"/>
-      <c r="P40" s="82"/>
-      <c r="Q40" s="82"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
       <c r="R40" s="51"/>
       <c r="S40" s="22"/>
       <c r="T40" s="23"/>
@@ -3297,11 +3309,11 @@
       <c r="AL40" s="10"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="53"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
+      <c r="A41" s="77"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
       <c r="F41" s="37" t="s">
         <v>14</v>
       </c>
@@ -3339,33 +3351,33 @@
       <c r="AL41" s="41"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="54">
+      <c r="A42" s="76">
         <v>3</v>
       </c>
-      <c r="B42" s="52" t="s">
+      <c r="B42" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="52">
+      <c r="C42" s="78">
         <v>4</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
       <c r="F42" s="21" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="24"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="82"/>
-      <c r="N42" s="82"/>
-      <c r="O42" s="82"/>
-      <c r="P42" s="94"/>
-      <c r="Q42" s="81"/>
-      <c r="R42" s="96"/>
-      <c r="S42" s="80"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="57"/>
+      <c r="P42" s="69"/>
+      <c r="Q42" s="56"/>
+      <c r="R42" s="71"/>
+      <c r="S42" s="55"/>
       <c r="T42" s="24"/>
       <c r="U42" s="24"/>
       <c r="V42" s="24"/>
@@ -3387,11 +3399,11 @@
       <c r="AL42" s="27"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="53"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
       <c r="F43" s="42" t="s">
         <v>14</v>
       </c>
@@ -3429,17 +3441,17 @@
       <c r="AL43" s="32"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="54">
+      <c r="A44" s="76">
         <v>4</v>
       </c>
-      <c r="B44" s="52" t="s">
-        <v>35</v>
+      <c r="B44" s="78" t="s">
+        <v>34</v>
       </c>
-      <c r="C44" s="52">
+      <c r="C44" s="78">
         <v>4</v>
       </c>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
       <c r="F44" s="33" t="s">
         <v>13</v>
       </c>
@@ -3453,10 +3465,10 @@
       <c r="N44" s="34"/>
       <c r="O44" s="34"/>
       <c r="P44" s="34"/>
-      <c r="Q44" s="91"/>
-      <c r="R44" s="99"/>
-      <c r="S44" s="77"/>
-      <c r="T44" s="78"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="74"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="53"/>
       <c r="U44" s="34"/>
       <c r="V44" s="34"/>
       <c r="W44" s="34"/>
@@ -3477,11 +3489,11 @@
       <c r="AL44" s="10"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="53"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
+      <c r="A45" s="77"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
       <c r="F45" s="37" t="s">
         <v>14</v>
       </c>
@@ -3519,13 +3531,13 @@
       <c r="AL45" s="41"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="54">
+      <c r="A46" s="76">
         <v>5</v>
       </c>
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3563,11 +3575,11 @@
       <c r="AL46" s="27"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
       <c r="F47" s="42" t="s">
         <v>14</v>
       </c>
@@ -3605,13 +3617,13 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="54">
+      <c r="A48" s="76">
         <v>6</v>
       </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
       <c r="F48" s="33" t="s">
         <v>13</v>
       </c>
@@ -3649,11 +3661,11 @@
       <c r="AL48" s="10"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
       <c r="F49" s="37" t="s">
         <v>14</v>
       </c>
@@ -3733,17 +3745,17 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="54">
+      <c r="A51" s="76">
         <v>1</v>
       </c>
-      <c r="B51" s="52" t="s">
+      <c r="B51" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="52">
+      <c r="C51" s="78">
         <v>8</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
       <c r="F51" s="21" t="s">
         <v>13</v>
       </c>
@@ -3755,14 +3767,14 @@
       <c r="L51" s="24"/>
       <c r="M51" s="24"/>
       <c r="N51" s="24"/>
-      <c r="O51" s="81"/>
-      <c r="P51" s="81"/>
-      <c r="Q51" s="81"/>
-      <c r="R51" s="93"/>
-      <c r="S51" s="94"/>
-      <c r="T51" s="82"/>
-      <c r="U51" s="82"/>
-      <c r="V51" s="82"/>
+      <c r="O51" s="56"/>
+      <c r="P51" s="56"/>
+      <c r="Q51" s="56"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="69"/>
+      <c r="T51" s="57"/>
+      <c r="U51" s="57"/>
+      <c r="V51" s="57"/>
       <c r="W51" s="24"/>
       <c r="X51" s="24"/>
       <c r="Y51" s="10"/>
@@ -3781,11 +3793,11 @@
       <c r="AL51" s="27"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="53"/>
-      <c r="B52" s="53"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="77"/>
       <c r="F52" s="28" t="s">
         <v>14</v>
       </c>
@@ -3823,17 +3835,17 @@
       <c r="AL52" s="32"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="54">
+      <c r="A53" s="76">
         <v>2</v>
       </c>
-      <c r="B53" s="52" t="s">
+      <c r="B53" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="52">
+      <c r="C53" s="78">
         <v>8</v>
       </c>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="78"/>
       <c r="F53" s="33" t="s">
         <v>13</v>
       </c>
@@ -3845,14 +3857,14 @@
       <c r="L53" s="34"/>
       <c r="M53" s="34"/>
       <c r="N53" s="34"/>
-      <c r="O53" s="81"/>
-      <c r="P53" s="81"/>
-      <c r="Q53" s="81"/>
-      <c r="R53" s="81"/>
-      <c r="S53" s="82"/>
-      <c r="T53" s="94"/>
-      <c r="U53" s="100"/>
-      <c r="V53" s="82"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="57"/>
+      <c r="T53" s="69"/>
+      <c r="U53" s="75"/>
+      <c r="V53" s="57"/>
       <c r="W53" s="34"/>
       <c r="X53" s="34"/>
       <c r="Y53" s="10"/>
@@ -3871,11 +3883,11 @@
       <c r="AL53" s="10"/>
     </row>
     <row r="54" spans="1:38" ht="12" customHeight="1">
-      <c r="A54" s="53"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="53"/>
-      <c r="E54" s="53"/>
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
       <c r="F54" s="37" t="s">
         <v>14</v>
       </c>
@@ -3913,17 +3925,17 @@
       <c r="AL54" s="41"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="54">
+      <c r="A55" s="76">
         <v>3</v>
       </c>
-      <c r="B55" s="52" t="s">
+      <c r="B55" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="C55" s="52">
+      <c r="C55" s="78">
         <v>4</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
       <c r="F55" s="21" t="s">
         <v>13</v>
       </c>
@@ -3936,14 +3948,14 @@
       <c r="M55" s="24"/>
       <c r="N55" s="24"/>
       <c r="O55" s="24"/>
-      <c r="P55" s="81"/>
-      <c r="Q55" s="81"/>
-      <c r="R55" s="96"/>
-      <c r="S55" s="80"/>
-      <c r="T55" s="81"/>
-      <c r="U55" s="81"/>
-      <c r="V55" s="93"/>
-      <c r="W55" s="81"/>
+      <c r="P55" s="56"/>
+      <c r="Q55" s="56"/>
+      <c r="R55" s="71"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="56"/>
+      <c r="U55" s="56"/>
+      <c r="V55" s="68"/>
+      <c r="W55" s="56"/>
       <c r="X55" s="24"/>
       <c r="Y55" s="10"/>
       <c r="Z55" s="10"/>
@@ -3961,11 +3973,11 @@
       <c r="AL55" s="27"/>
     </row>
     <row r="56" spans="1:38" ht="12" customHeight="1">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
       <c r="F56" s="42" t="s">
         <v>14</v>
       </c>
@@ -4003,13 +4015,13 @@
       <c r="AL56" s="32"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="54">
+      <c r="A57" s="76">
         <v>4</v>
       </c>
-      <c r="B57" s="52"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
       <c r="F57" s="33" t="s">
         <v>13</v>
       </c>
@@ -4047,11 +4059,11 @@
       <c r="AL57" s="10"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="53"/>
-      <c r="B58" s="53"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
       <c r="F58" s="37" t="s">
         <v>14</v>
       </c>
@@ -4089,13 +4101,13 @@
       <c r="AL58" s="41"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="54">
+      <c r="A59" s="76">
         <v>5</v>
       </c>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4133,11 +4145,11 @@
       <c r="AL59" s="27"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="53"/>
-      <c r="B60" s="53"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="53"/>
-      <c r="E60" s="53"/>
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="77"/>
       <c r="F60" s="42" t="s">
         <v>14</v>
       </c>
@@ -4175,13 +4187,13 @@
       <c r="AL60" s="46"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="54">
+      <c r="A61" s="76">
         <v>6</v>
       </c>
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
-      <c r="D61" s="52"/>
-      <c r="E61" s="52"/>
+      <c r="B61" s="78"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="78"/>
       <c r="F61" s="33" t="s">
         <v>13</v>
       </c>
@@ -4219,11 +4231,11 @@
       <c r="AL61" s="10"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="53"/>
-      <c r="B62" s="53"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="77"/>
       <c r="F62" s="37" t="s">
         <v>14</v>
       </c>
@@ -4303,13 +4315,13 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="54">
+      <c r="A64" s="76">
         <v>1</v>
       </c>
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
+      <c r="B64" s="78"/>
+      <c r="C64" s="78"/>
+      <c r="D64" s="78"/>
+      <c r="E64" s="78"/>
       <c r="F64" s="21" t="s">
         <v>13</v>
       </c>
@@ -4347,11 +4359,11 @@
       <c r="AL64" s="27"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="53"/>
-      <c r="B65" s="53"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="53"/>
-      <c r="E65" s="53"/>
+      <c r="A65" s="77"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="77"/>
+      <c r="D65" s="77"/>
+      <c r="E65" s="77"/>
       <c r="F65" s="28" t="s">
         <v>14</v>
       </c>
@@ -4389,13 +4401,13 @@
       <c r="AL65" s="32"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="54">
+      <c r="A66" s="76">
         <v>2</v>
       </c>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
+      <c r="B66" s="78"/>
+      <c r="C66" s="78"/>
+      <c r="D66" s="78"/>
+      <c r="E66" s="78"/>
       <c r="F66" s="33" t="s">
         <v>13</v>
       </c>
@@ -4433,11 +4445,11 @@
       <c r="AL66" s="10"/>
     </row>
     <row r="67" spans="1:38" ht="12" customHeight="1">
-      <c r="A67" s="53"/>
-      <c r="B67" s="53"/>
-      <c r="C67" s="53"/>
-      <c r="D67" s="53"/>
-      <c r="E67" s="53"/>
+      <c r="A67" s="77"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="77"/>
+      <c r="D67" s="77"/>
+      <c r="E67" s="77"/>
       <c r="F67" s="37" t="s">
         <v>14</v>
       </c>
@@ -4475,13 +4487,13 @@
       <c r="AL67" s="41"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="54">
+      <c r="A68" s="76">
         <v>3</v>
       </c>
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
+      <c r="B68" s="78"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="78"/>
+      <c r="E68" s="78"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4519,11 +4531,11 @@
       <c r="AL68" s="27"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="53"/>
-      <c r="B69" s="53"/>
-      <c r="C69" s="53"/>
-      <c r="D69" s="53"/>
-      <c r="E69" s="53"/>
+      <c r="A69" s="77"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
       <c r="F69" s="42" t="s">
         <v>14</v>
       </c>
@@ -4561,13 +4573,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="54">
+      <c r="A70" s="76">
         <v>4</v>
       </c>
-      <c r="B70" s="52"/>
-      <c r="C70" s="52"/>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4605,11 +4617,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="53"/>
-      <c r="B71" s="53"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="53"/>
-      <c r="E71" s="53"/>
+      <c r="A71" s="77"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
       <c r="F71" s="37" t="s">
         <v>14</v>
       </c>
@@ -4647,13 +4659,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="54">
+      <c r="A72" s="76">
         <v>5</v>
       </c>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -4691,11 +4703,11 @@
       <c r="AL72" s="27"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="53"/>
-      <c r="B73" s="53"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
+      <c r="A73" s="77"/>
+      <c r="B73" s="77"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
       <c r="F73" s="42" t="s">
         <v>14</v>
       </c>
@@ -4733,13 +4745,13 @@
       <c r="AL73" s="46"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="54">
+      <c r="A74" s="76">
         <v>6</v>
       </c>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -4777,11 +4789,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="53"/>
-      <c r="B75" s="53"/>
-      <c r="C75" s="53"/>
-      <c r="D75" s="53"/>
-      <c r="E75" s="53"/>
+      <c r="A75" s="77"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="77"/>
       <c r="F75" s="37" t="s">
         <v>14</v>
       </c>
@@ -4859,13 +4871,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="54">
+      <c r="A77" s="76">
         <v>1</v>
       </c>
-      <c r="B77" s="52"/>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -4903,11 +4915,11 @@
       <c r="AL77" s="27"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="53"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
+      <c r="A78" s="77"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="77"/>
+      <c r="E78" s="77"/>
       <c r="F78" s="28" t="s">
         <v>14</v>
       </c>
@@ -4945,13 +4957,13 @@
       <c r="AL78" s="32"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="54">
+      <c r="A79" s="76">
         <v>2</v>
       </c>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
+      <c r="B79" s="78"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
       <c r="F79" s="33" t="s">
         <v>13</v>
       </c>
@@ -4989,11 +5001,11 @@
       <c r="AL79" s="10"/>
     </row>
     <row r="80" spans="1:38" ht="12" customHeight="1">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
+      <c r="A80" s="77"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
       <c r="F80" s="37" t="s">
         <v>14</v>
       </c>
@@ -5031,13 +5043,13 @@
       <c r="AL80" s="41"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="54">
+      <c r="A81" s="76">
         <v>3</v>
       </c>
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
+      <c r="B81" s="78"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
+      <c r="E81" s="78"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5075,11 +5087,11 @@
       <c r="AL81" s="27"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="53"/>
-      <c r="B82" s="53"/>
-      <c r="C82" s="53"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="53"/>
+      <c r="A82" s="77"/>
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="77"/>
+      <c r="E82" s="77"/>
       <c r="F82" s="42" t="s">
         <v>14</v>
       </c>
@@ -5117,13 +5129,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="54">
+      <c r="A83" s="76">
         <v>4</v>
       </c>
-      <c r="B83" s="52"/>
-      <c r="C83" s="52"/>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
+      <c r="B83" s="78"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="78"/>
+      <c r="E83" s="78"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -5161,11 +5173,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="53"/>
-      <c r="B84" s="53"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="53"/>
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="77"/>
+      <c r="E84" s="77"/>
       <c r="F84" s="42" t="s">
         <v>14</v>
       </c>
@@ -41844,16 +41856,177 @@
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C51:C52"/>
@@ -41878,177 +42051,16 @@
     <mergeCell ref="D59:D60"/>
     <mergeCell ref="E59:E60"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
@@ -42057,6 +42069,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.70866141732283516" right="0.70866141732283516" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/進捗管理表/進捗管理表_富.xlsx
+++ b/進捗管理表/進捗管理表_富.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN02\Documents\project\MyTaskSystem\進捗管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6EEA66-4010-44A6-8EF3-349E7CA4C651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF00B10-ECC6-47A0-A255-F883F4A12A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4365" yWindow="3390" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小工程" sheetId="1" r:id="rId1"/>
@@ -289,6 +289,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -335,6 +337,8 @@
       <sz val="11"/>
       <color theme="4"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="9">
@@ -382,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -972,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1201,23 +1205,44 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1255,31 +1280,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,142 +1592,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="81" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="85">
+      <c r="G3" s="92">
         <v>45705</v>
       </c>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86"/>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="86"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="86"/>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86"/>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="87"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
+      <c r="AF3" s="93"/>
+      <c r="AG3" s="93"/>
+      <c r="AH3" s="93"/>
+      <c r="AI3" s="93"/>
+      <c r="AJ3" s="93"/>
+      <c r="AK3" s="93"/>
+      <c r="AL3" s="94"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="97" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="100" t="s">
+      <c r="E4" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="90"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="96"/>
+      <c r="W4" s="96"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="96"/>
+      <c r="AF4" s="96"/>
+      <c r="AG4" s="96"/>
+      <c r="AH4" s="96"/>
+      <c r="AI4" s="96"/>
+      <c r="AJ4" s="96"/>
+      <c r="AK4" s="96"/>
+      <c r="AL4" s="97"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="95"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="79">
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="87">
         <v>17</v>
       </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81">
+      <c r="H5" s="88"/>
+      <c r="I5" s="83">
         <v>18</v>
       </c>
-      <c r="J5" s="98"/>
-      <c r="K5" s="81">
+      <c r="J5" s="84"/>
+      <c r="K5" s="83">
         <v>19</v>
       </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="81">
+      <c r="L5" s="84"/>
+      <c r="M5" s="83">
         <v>20</v>
       </c>
-      <c r="N5" s="98"/>
-      <c r="O5" s="81">
+      <c r="N5" s="84"/>
+      <c r="O5" s="83">
         <v>21</v>
       </c>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="81">
+      <c r="P5" s="84"/>
+      <c r="Q5" s="83">
         <v>25</v>
       </c>
-      <c r="R5" s="99"/>
-      <c r="S5" s="79">
+      <c r="R5" s="85"/>
+      <c r="S5" s="87">
         <v>26</v>
       </c>
-      <c r="T5" s="80"/>
-      <c r="U5" s="81">
+      <c r="T5" s="88"/>
+      <c r="U5" s="83">
         <v>27</v>
       </c>
-      <c r="V5" s="80"/>
-      <c r="W5" s="81">
+      <c r="V5" s="88"/>
+      <c r="W5" s="83">
         <v>28</v>
       </c>
-      <c r="X5" s="80"/>
+      <c r="X5" s="88"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1748,43 +1749,43 @@
       <c r="C6" s="77"/>
       <c r="D6" s="77"/>
       <c r="E6" s="77"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="79" t="s">
+      <c r="F6" s="91"/>
+      <c r="G6" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="91" t="s">
+      <c r="H6" s="88"/>
+      <c r="I6" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="80"/>
-      <c r="K6" s="81" t="s">
+      <c r="J6" s="88"/>
+      <c r="K6" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="80"/>
-      <c r="M6" s="81" t="s">
+      <c r="L6" s="88"/>
+      <c r="M6" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="81" t="s">
+      <c r="N6" s="88"/>
+      <c r="O6" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="81" t="s">
+      <c r="P6" s="88"/>
+      <c r="Q6" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="80"/>
-      <c r="S6" s="92" t="s">
+      <c r="R6" s="88"/>
+      <c r="S6" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="80"/>
-      <c r="U6" s="93" t="s">
+      <c r="T6" s="88"/>
+      <c r="U6" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="80"/>
-      <c r="W6" s="93" t="s">
+      <c r="V6" s="88"/>
+      <c r="W6" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="80"/>
+      <c r="X6" s="88"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -1843,13 +1844,13 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="76">
+      <c r="A8" s="78">
         <v>1</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
       <c r="F8" s="21" t="s">
         <v>13</v>
       </c>
@@ -1929,13 +1930,13 @@
       <c r="AL9" s="32"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A10" s="76">
+      <c r="A10" s="78">
         <v>2</v>
       </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
       <c r="F10" s="33" t="s">
         <v>13</v>
       </c>
@@ -2015,13 +2016,13 @@
       <c r="AL11" s="41"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A12" s="76">
+      <c r="A12" s="78">
         <v>3</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
       <c r="F12" s="21" t="s">
         <v>13</v>
       </c>
@@ -2101,13 +2102,13 @@
       <c r="AL13" s="32"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A14" s="76">
+      <c r="A14" s="78">
         <v>4</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
       <c r="F14" s="33" t="s">
         <v>13</v>
       </c>
@@ -2187,13 +2188,13 @@
       <c r="AL15" s="41"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A16" s="76">
+      <c r="A16" s="78">
         <v>5</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
       <c r="F16" s="21" t="s">
         <v>13</v>
       </c>
@@ -2273,13 +2274,13 @@
       <c r="AL17" s="46"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A18" s="76">
+      <c r="A18" s="78">
         <v>6</v>
       </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
       <c r="F18" s="33" t="s">
         <v>13</v>
       </c>
@@ -2359,13 +2360,13 @@
       <c r="AL19" s="46"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A20" s="76">
+      <c r="A20" s="78">
         <v>7</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
       <c r="F20" s="33" t="s">
         <v>13</v>
       </c>
@@ -2445,13 +2446,13 @@
       <c r="AL21" s="46"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A22" s="76">
+      <c r="A22" s="78">
         <v>8</v>
       </c>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
       <c r="F22" s="21" t="s">
         <v>13</v>
       </c>
@@ -2573,19 +2574,19 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="78">
         <v>1</v>
       </c>
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="78">
+      <c r="C25" s="76">
         <v>4</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="76" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -2667,19 +2668,19 @@
       <c r="AL26" s="32"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="76">
+      <c r="A27" s="78">
         <v>2</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="78">
+      <c r="C27" s="76">
         <v>4</v>
       </c>
-      <c r="D27" s="78" t="s">
+      <c r="D27" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="78" t="s">
+      <c r="E27" s="76" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="33" t="s">
@@ -2730,7 +2731,7 @@
       <c r="G28" s="38"/>
       <c r="H28" s="39"/>
       <c r="I28" s="39"/>
-      <c r="J28" s="102"/>
+      <c r="J28" s="101"/>
       <c r="K28" s="59"/>
       <c r="L28" s="59"/>
       <c r="M28" s="59"/>
@@ -2761,19 +2762,19 @@
       <c r="AL28" s="41"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="78">
         <v>3</v>
       </c>
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="78">
+      <c r="C29" s="76">
         <v>2</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="78" t="s">
+      <c r="E29" s="76" t="s">
         <v>36</v>
       </c>
       <c r="F29" s="21" t="s">
@@ -2825,7 +2826,7 @@
       <c r="H30" s="44"/>
       <c r="I30" s="44"/>
       <c r="J30" s="44"/>
-      <c r="K30" s="102"/>
+      <c r="K30" s="101"/>
       <c r="L30" s="44"/>
       <c r="M30" s="44"/>
       <c r="N30" s="44"/>
@@ -2855,19 +2856,19 @@
       <c r="AL30" s="32"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="78">
         <v>4</v>
       </c>
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="78">
+      <c r="C31" s="76">
         <v>2</v>
       </c>
-      <c r="D31" s="78" t="s">
+      <c r="D31" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="78" t="s">
+      <c r="E31" s="76" t="s">
         <v>36</v>
       </c>
       <c r="F31" s="33" t="s">
@@ -2919,7 +2920,7 @@
       <c r="H32" s="39"/>
       <c r="I32" s="39"/>
       <c r="J32" s="39"/>
-      <c r="K32" s="102"/>
+      <c r="K32" s="101"/>
       <c r="L32" s="39"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
@@ -2949,19 +2950,19 @@
       <c r="AL32" s="41"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="78">
         <v>5</v>
       </c>
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="76">
         <v>2</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="78" t="s">
+      <c r="E33" s="76" t="s">
         <v>36</v>
       </c>
       <c r="F33" s="21" t="s">
@@ -3013,7 +3014,7 @@
       <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
-      <c r="K34" s="102"/>
+      <c r="K34" s="101"/>
       <c r="L34" s="30"/>
       <c r="M34" s="30"/>
       <c r="N34" s="30"/>
@@ -3043,13 +3044,13 @@
       <c r="AL34" s="46"/>
     </row>
     <row r="35" spans="1:38" ht="12.75" customHeight="1">
-      <c r="A35" s="76">
+      <c r="A35" s="78">
         <v>6</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
       <c r="F35" s="33" t="s">
         <v>13</v>
       </c>
@@ -3171,17 +3172,17 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="76">
+      <c r="A38" s="78">
         <v>1</v>
       </c>
-      <c r="B38" s="78" t="s">
+      <c r="B38" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="78">
+      <c r="C38" s="76">
         <v>8</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
       <c r="F38" s="21" t="s">
         <v>13</v>
       </c>
@@ -3261,17 +3262,17 @@
       <c r="AL39" s="32"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="76">
+      <c r="A40" s="78">
         <v>2</v>
       </c>
-      <c r="B40" s="78" t="s">
+      <c r="B40" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="78">
+      <c r="C40" s="76">
         <v>8</v>
       </c>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
       <c r="F40" s="33" t="s">
         <v>13</v>
       </c>
@@ -3351,17 +3352,17 @@
       <c r="AL41" s="41"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="76">
+      <c r="A42" s="78">
         <v>3</v>
       </c>
-      <c r="B42" s="78" t="s">
+      <c r="B42" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="78">
+      <c r="C42" s="76">
         <v>4</v>
       </c>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
       <c r="F42" s="21" t="s">
         <v>13</v>
       </c>
@@ -3441,17 +3442,17 @@
       <c r="AL43" s="32"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="76">
+      <c r="A44" s="78">
         <v>4</v>
       </c>
-      <c r="B44" s="78" t="s">
+      <c r="B44" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="78">
+      <c r="C44" s="76">
         <v>4</v>
       </c>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
       <c r="F44" s="33" t="s">
         <v>13</v>
       </c>
@@ -3531,13 +3532,13 @@
       <c r="AL45" s="41"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="76">
+      <c r="A46" s="78">
         <v>5</v>
       </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3617,13 +3618,13 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="76">
+      <c r="A48" s="78">
         <v>6</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
       <c r="F48" s="33" t="s">
         <v>13</v>
       </c>
@@ -3745,17 +3746,17 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="76">
+      <c r="A51" s="78">
         <v>1</v>
       </c>
-      <c r="B51" s="78" t="s">
+      <c r="B51" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="78">
+      <c r="C51" s="76">
         <v>8</v>
       </c>
-      <c r="D51" s="78"/>
-      <c r="E51" s="78"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
       <c r="F51" s="21" t="s">
         <v>13</v>
       </c>
@@ -3835,17 +3836,17 @@
       <c r="AL52" s="32"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="76">
+      <c r="A53" s="78">
         <v>2</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="78">
+      <c r="C53" s="76">
         <v>8</v>
       </c>
-      <c r="D53" s="78"/>
-      <c r="E53" s="78"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
       <c r="F53" s="33" t="s">
         <v>13</v>
       </c>
@@ -3925,17 +3926,17 @@
       <c r="AL54" s="41"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="76">
+      <c r="A55" s="78">
         <v>3</v>
       </c>
-      <c r="B55" s="78" t="s">
+      <c r="B55" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="C55" s="78">
+      <c r="C55" s="76">
         <v>4</v>
       </c>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="76"/>
       <c r="F55" s="21" t="s">
         <v>13</v>
       </c>
@@ -4015,13 +4016,13 @@
       <c r="AL56" s="32"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="76">
+      <c r="A57" s="78">
         <v>4</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="76"/>
+      <c r="E57" s="76"/>
       <c r="F57" s="33" t="s">
         <v>13</v>
       </c>
@@ -4101,13 +4102,13 @@
       <c r="AL58" s="41"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="76">
+      <c r="A59" s="78">
         <v>5</v>
       </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="78"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="76"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4187,13 +4188,13 @@
       <c r="AL60" s="46"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="76">
+      <c r="A61" s="78">
         <v>6</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
       <c r="F61" s="33" t="s">
         <v>13</v>
       </c>
@@ -4315,13 +4316,13 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="76">
+      <c r="A64" s="78">
         <v>1</v>
       </c>
-      <c r="B64" s="78"/>
-      <c r="C64" s="78"/>
-      <c r="D64" s="78"/>
-      <c r="E64" s="78"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
+      <c r="E64" s="76"/>
       <c r="F64" s="21" t="s">
         <v>13</v>
       </c>
@@ -4401,13 +4402,13 @@
       <c r="AL65" s="32"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="76">
+      <c r="A66" s="78">
         <v>2</v>
       </c>
-      <c r="B66" s="78"/>
-      <c r="C66" s="78"/>
-      <c r="D66" s="78"/>
-      <c r="E66" s="78"/>
+      <c r="B66" s="76"/>
+      <c r="C66" s="76"/>
+      <c r="D66" s="76"/>
+      <c r="E66" s="76"/>
       <c r="F66" s="33" t="s">
         <v>13</v>
       </c>
@@ -4487,13 +4488,13 @@
       <c r="AL67" s="41"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="76">
+      <c r="A68" s="78">
         <v>3</v>
       </c>
-      <c r="B68" s="78"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="78"/>
-      <c r="E68" s="78"/>
+      <c r="B68" s="76"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="76"/>
+      <c r="E68" s="76"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4573,13 +4574,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="76">
+      <c r="A70" s="78">
         <v>4</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="78"/>
-      <c r="D70" s="78"/>
-      <c r="E70" s="78"/>
+      <c r="B70" s="76"/>
+      <c r="C70" s="76"/>
+      <c r="D70" s="76"/>
+      <c r="E70" s="76"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4659,13 +4660,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="76">
+      <c r="A72" s="78">
         <v>5</v>
       </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="76"/>
+      <c r="D72" s="76"/>
+      <c r="E72" s="76"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -4745,13 +4746,13 @@
       <c r="AL73" s="46"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="76">
+      <c r="A74" s="78">
         <v>6</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="78"/>
-      <c r="D74" s="78"/>
-      <c r="E74" s="78"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
+      <c r="E74" s="76"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -4871,13 +4872,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="76">
+      <c r="A77" s="78">
         <v>1</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="78"/>
-      <c r="D77" s="78"/>
-      <c r="E77" s="78"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="76"/>
+      <c r="D77" s="76"/>
+      <c r="E77" s="76"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -4957,13 +4958,13 @@
       <c r="AL78" s="32"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="76">
+      <c r="A79" s="78">
         <v>2</v>
       </c>
-      <c r="B79" s="78"/>
-      <c r="C79" s="78"/>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
+      <c r="B79" s="76"/>
+      <c r="C79" s="76"/>
+      <c r="D79" s="76"/>
+      <c r="E79" s="76"/>
       <c r="F79" s="33" t="s">
         <v>13</v>
       </c>
@@ -5043,13 +5044,13 @@
       <c r="AL80" s="41"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="76">
+      <c r="A81" s="78">
         <v>3</v>
       </c>
-      <c r="B81" s="78"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="78"/>
-      <c r="E81" s="78"/>
+      <c r="B81" s="76"/>
+      <c r="C81" s="76"/>
+      <c r="D81" s="76"/>
+      <c r="E81" s="76"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5129,13 +5130,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="76">
+      <c r="A83" s="78">
         <v>4</v>
       </c>
-      <c r="B83" s="78"/>
-      <c r="C83" s="78"/>
-      <c r="D83" s="78"/>
-      <c r="E83" s="78"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="76"/>
+      <c r="E83" s="76"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -41856,21 +41857,172 @@
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="A31:A32"/>
@@ -41895,172 +42047,21 @@
     <mergeCell ref="D44:D45"/>
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
